--- a/data/trans_orig/IQ23_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72869</t>
+          <t>71829</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86876</t>
+          <t>85804</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64600</t>
+          <t>65561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79145</t>
+          <t>79110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141944</t>
+          <t>141551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>161931</t>
+          <t>160974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17028</t>
+          <t>18100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31035</t>
+          <t>32075</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>18435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32945</t>
+          <t>31984</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39519</t>
+          <t>40476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59506</t>
+          <t>59899</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57976</t>
+          <t>57489</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71121</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54935</t>
+          <t>54739</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68234</t>
+          <t>68031</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116760</t>
+          <t>117616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>135568</t>
+          <t>135422</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15499</t>
+          <t>15964</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28644</t>
+          <t>29131</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29857</t>
+          <t>30053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35844</t>
+          <t>35990</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54652</t>
+          <t>53796</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40610</t>
+          <t>40039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52763</t>
+          <t>52760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65988</t>
+          <t>66106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80391</t>
+          <t>79998</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110456</t>
+          <t>111551</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129781</t>
+          <t>129768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>27353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18254</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32657</t>
+          <t>32539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36257</t>
+          <t>36270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55582</t>
+          <t>54487</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131300</t>
+          <t>131168</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151578</t>
+          <t>151797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>142095</t>
+          <t>142405</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162203</t>
+          <t>160850</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>280199</t>
+          <t>278707</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308500</t>
+          <t>308361</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,09%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46340</t>
+          <t>46121</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66618</t>
+          <t>66750</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39871</t>
+          <t>41224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59979</t>
+          <t>59669</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91492</t>
+          <t>91631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119793</t>
+          <t>121285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66823</t>
+          <t>67028</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80915</t>
+          <t>81211</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86618</t>
+          <t>87020</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102390</t>
+          <t>102025</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>156785</t>
+          <t>158071</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>179049</t>
+          <t>179359</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22589</t>
+          <t>22293</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36681</t>
+          <t>36476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23542</t>
+          <t>23907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39314</t>
+          <t>38912</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50387</t>
+          <t>50077</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72651</t>
+          <t>71365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52918</t>
+          <t>52373</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64078</t>
+          <t>63584</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44387</t>
+          <t>44138</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56659</t>
+          <t>57057</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100238</t>
+          <t>100731</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>117425</t>
+          <t>118057</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,59%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10022</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21182</t>
+          <t>21727</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28005</t>
+          <t>28254</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29068</t>
+          <t>28436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46255</t>
+          <t>45762</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>450372</t>
+          <t>449371</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>485710</t>
+          <t>482974</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>486578</t>
+          <t>484223</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>523604</t>
+          <t>521804</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>946327</t>
+          <t>948784</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>996460</t>
+          <t>997198</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>147728</t>
+          <t>150464</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>183066</t>
+          <t>184067</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>157778</t>
+          <t>159578</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>194804</t>
+          <t>197159</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>318360</t>
+          <t>317622</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>368493</t>
+          <t>366036</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62894</t>
+          <t>63458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76033</t>
+          <t>76431</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52907</t>
+          <t>53349</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67473</t>
+          <t>68207</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>122661</t>
+          <t>121236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140332</t>
+          <t>140059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,94%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>26475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22290</t>
+          <t>21556</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36856</t>
+          <t>36414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>39638</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57036</t>
+          <t>58461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63378</t>
+          <t>62958</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76850</t>
+          <t>77427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65272</t>
+          <t>64950</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78905</t>
+          <t>79300</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>133044</t>
+          <t>133947</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152756</t>
+          <t>153561</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,8%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16416</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29888</t>
+          <t>30308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>17478</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31506</t>
+          <t>31828</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37288</t>
+          <t>36483</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57000</t>
+          <t>56097</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52505</t>
+          <t>52332</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66051</t>
+          <t>66835</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56420</t>
+          <t>55115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69282</t>
+          <t>68794</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112364</t>
+          <t>113887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132248</t>
+          <t>132625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>19322</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33652</t>
+          <t>33825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>17428</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29802</t>
+          <t>31107</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40131</t>
+          <t>39754</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60015</t>
+          <t>58492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>130035</t>
+          <t>129905</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151482</t>
+          <t>151361</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>147287</t>
+          <t>147590</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171914</t>
+          <t>170976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>284572</t>
+          <t>285056</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316139</t>
+          <t>315614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53164</t>
+          <t>53285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74611</t>
+          <t>74741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55524</t>
+          <t>56462</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80151</t>
+          <t>79848</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115944</t>
+          <t>116469</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147511</t>
+          <t>147027</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96781</t>
+          <t>96797</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115484</t>
+          <t>115037</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83578</t>
+          <t>83002</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101715</t>
+          <t>102462</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>187659</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>212802</t>
+          <t>212045</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,06%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33685</t>
+          <t>34132</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52388</t>
+          <t>52372</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39342</t>
+          <t>38595</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57479</t>
+          <t>58055</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>77424</t>
+          <t>78181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>102567</t>
+          <t>103324</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34484</t>
+          <t>33769</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44772</t>
+          <t>44545</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54527</t>
+          <t>54270</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65579</t>
+          <t>65061</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92226</t>
+          <t>92185</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106883</t>
+          <t>107281</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9139</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19427</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19511</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21066</t>
+          <t>20668</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35723</t>
+          <t>35764</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>470260</t>
+          <t>468351</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>507746</t>
+          <t>506280</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>491903</t>
+          <t>491489</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>533598</t>
+          <t>530364</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>973533</t>
+          <t>973260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1026898</t>
+          <t>1027512</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,8%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>169336</t>
+          <t>170802</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206822</t>
+          <t>208731</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>181699</t>
+          <t>184933</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>223394</t>
+          <t>223808</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>365481</t>
+          <t>364867</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>418846</t>
+          <t>419119</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38828</t>
+          <t>39346</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53460</t>
+          <t>54249</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59468</t>
+          <t>60073</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74586</t>
+          <t>74977</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103414</t>
+          <t>104171</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124282</t>
+          <t>125333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28368</t>
+          <t>27579</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43000</t>
+          <t>42482</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40329</t>
+          <t>39724</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57343</t>
+          <t>56292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78211</t>
+          <t>77454</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69915</t>
+          <t>70454</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84185</t>
+          <t>84081</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65257</t>
+          <t>65273</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81553</t>
+          <t>81439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>139484</t>
+          <t>139886</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>160634</t>
+          <t>161305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,87%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20395</t>
+          <t>20499</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34665</t>
+          <t>34126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29309</t>
+          <t>29423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45605</t>
+          <t>45589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54808</t>
+          <t>54137</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75958</t>
+          <t>75556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35843</t>
+          <t>36415</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47695</t>
+          <t>47229</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43810</t>
+          <t>44006</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56691</t>
+          <t>56562</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83862</t>
+          <t>85018</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101589</t>
+          <t>101793</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,49%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25997</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29192</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33253</t>
+          <t>33049</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50980</t>
+          <t>49824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>135670</t>
+          <t>136477</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>158607</t>
+          <t>158705</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121873</t>
+          <t>122002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144844</t>
+          <t>145102</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>264364</t>
+          <t>263283</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295572</t>
+          <t>295149</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62936</t>
+          <t>62838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85873</t>
+          <t>85066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63717</t>
+          <t>63459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86688</t>
+          <t>86559</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134532</t>
+          <t>134955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165740</t>
+          <t>166821</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91221</t>
+          <t>90509</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107372</t>
+          <t>107545</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87845</t>
+          <t>87939</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106149</t>
+          <t>107601</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183449</t>
+          <t>184369</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>209062</t>
+          <t>208018</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,67%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28134</t>
+          <t>27961</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44285</t>
+          <t>44997</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36939</t>
+          <t>35487</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55243</t>
+          <t>55149</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69533</t>
+          <t>70577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95146</t>
+          <t>94226</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37444</t>
+          <t>37755</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49290</t>
+          <t>49586</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36471</t>
+          <t>35867</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49673</t>
+          <t>49238</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78250</t>
+          <t>77307</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>95412</t>
+          <t>95423</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23643</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>18587</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31354</t>
+          <t>31958</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>33489</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50662</t>
+          <t>51605</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>40,03%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>435548</t>
+          <t>438022</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>476522</t>
+          <t>477963</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>445535</t>
+          <t>444923</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>487235</t>
+          <t>485087</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>890706</t>
+          <t>894230</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>951022</t>
+          <t>953874</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,65%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>189862</t>
+          <t>188421</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>230836</t>
+          <t>228362</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>215900</t>
+          <t>218048</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>257600</t>
+          <t>258212</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>418497</t>
+          <t>415645</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>478813</t>
+          <t>475289</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65613</t>
+          <t>65317</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80367</t>
+          <t>80951</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91069</t>
+          <t>90936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110957</t>
+          <t>109908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>162914</t>
+          <t>162471</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>186526</t>
+          <t>186174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23374</t>
+          <t>22790</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>38424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>25399</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44238</t>
+          <t>44371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52522</t>
+          <t>52874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76134</t>
+          <t>76577</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60502</t>
+          <t>59641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74599</t>
+          <t>73910</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65962</t>
+          <t>65059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80159</t>
+          <t>79715</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130072</t>
+          <t>128948</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149698</t>
+          <t>150165</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,93%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20082</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34179</t>
+          <t>35040</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15414</t>
+          <t>15858</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29611</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>40089</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60182</t>
+          <t>61306</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32119</t>
+          <t>31890</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42632</t>
+          <t>42752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35540</t>
+          <t>35319</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49132</t>
+          <t>48815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71626</t>
+          <t>69970</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88883</t>
+          <t>88708</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,66%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19742</t>
+          <t>19971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28313</t>
+          <t>28534</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26831</t>
+          <t>27006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44088</t>
+          <t>45744</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138932</t>
+          <t>138432</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>177247</t>
+          <t>176176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127373</t>
+          <t>128429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>155457</t>
+          <t>156425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275631</t>
+          <t>274330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>324848</t>
+          <t>324000</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,59%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39262</t>
+          <t>40333</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77577</t>
+          <t>78077</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62419</t>
+          <t>61451</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90503</t>
+          <t>89447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109537</t>
+          <t>110385</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>158754</t>
+          <t>160055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71024</t>
+          <t>71213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89730</t>
+          <t>89659</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102272</t>
+          <t>103364</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>126619</t>
+          <t>127696</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>181298</t>
+          <t>181015</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>210067</t>
+          <t>211730</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>27685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46320</t>
+          <t>46131</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35998</t>
+          <t>34921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60345</t>
+          <t>59253</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69894</t>
+          <t>68231</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98663</t>
+          <t>98946</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44042</t>
+          <t>43808</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55365</t>
+          <t>55748</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40210</t>
+          <t>40409</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54847</t>
+          <t>55205</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88794</t>
+          <t>88296</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>106454</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23477</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17156</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31793</t>
+          <t>31594</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32034</t>
+          <t>33068</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50728</t>
+          <t>51226</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>441280</t>
+          <t>443270</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>492589</t>
+          <t>493592</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>497648</t>
+          <t>498408</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>545864</t>
+          <t>545413</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>951507</t>
+          <t>955336</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1019196</t>
+          <t>1026684</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>159067</t>
+          <t>158064</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>210376</t>
+          <t>208386</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>201365</t>
+          <t>201816</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>249581</t>
+          <t>248821</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>379689</t>
+          <t>372201</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>447378</t>
+          <t>443549</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
